--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -10,121 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>UI table</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>SortOrder</t>
-  </si>
-  <si>
-    <t>UIPrefab</t>
-  </si>
-  <si>
-    <t>PauseCoveredUI</t>
-  </si>
-  <si>
-    <t>UIGroupId</t>
-  </si>
-  <si>
-    <t>EscapeClose</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Display order relative to group</t>
-  </si>
-  <si>
-    <t>UI prefab name</t>
-  </si>
-  <si>
-    <t>Hide covered UI in the same group</t>
-  </si>
-  <si>
-    <t>UI group id</t>
-  </si>
-  <si>
-    <t>Allow close by back input</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Totem first slice: main menu</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>MainMenu</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Totem first slice: character select</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>CharacterSelect</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Totem first slice: startup selection</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>StartupSelect</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Totem first slice: combat HUD</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>CombatHUD</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -132,24 +20,24 @@
   <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -168,8 +56,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -537,212 +425,603 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" bestFit="1" width="13.125" customWidth="1"/>
-    <col min="3" max="3" bestFit="1" width="15.125" customWidth="1"/>
-    <col min="4" max="4" bestFit="1" width="40.125" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" bestFit="1" width="25.5" customWidth="1"/>
-    <col min="7" max="7" bestFit="1" width="10.5" customWidth="1"/>
-    <col min="8" max="8" bestFit="1" width="19.25" customWidth="1"/>
+    <col width="13.125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="15.125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="40.125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="25.5" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="19.25" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UI table</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>8</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SortOrder</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UIPrefab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PauseCoveredUI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>UIGroupId</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EscapeClose</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>11</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>17</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Display order relative to group</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UI prefab name</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Hide covered UI in the same group</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>UI group id</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Allow close by back input</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>23</v>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Totem first slice: main menu</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MainMenu</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>22</v>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Totem first slice: character select</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CharacterSelect</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>22</v>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Totem first slice: startup selection</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>StartupSelect</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>23</v>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Totem first slice: combat HUD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CombatHUD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Totem overlay: shop</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Totem overlay: three choices</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ThreeChoice</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Totem overlay: tattoo studio</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TattooStudio</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Totem overlay: pause menu</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PauseMenu</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Totem overlay: run result</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RunResult</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Totem overlay: settings</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Totem overlay: self tattoo</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SelfTattoo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Totem overlay: tattoo enchant</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TattooEnchant</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -752,10 +1031,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -765,9 +1044,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/GameData/DataTables/Core/UITable.xlsx
+++ b/GameData/DataTables/Core/UITable.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>#</t>
   </si>
@@ -89,99 +89,45 @@
     <t>false</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Totem first slice: character select</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Totem first slice: combat HUD</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>CombatHUD</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Totem overlay: pause menu</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>PauseMenu</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Totem overlay: run result</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>RunResult</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>CharacterSelect</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Totem first slice: startup selection</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>StartupSelect</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Totem first slice: combat HUD</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>CombatHUD</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Totem overlay: shop</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Shop</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Totem overlay: three choices</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>ThreeChoice</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Totem overlay: tattoo studio</t>
-  </si>
-  <si>
-    <t>TattooStudio</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Totem overlay: pause menu</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>PauseMenu</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Totem overlay: run result</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>RunResult</t>
-  </si>
-  <si>
     <t>Totem overlay: settings</t>
   </si>
   <si>
@@ -189,27 +135,6 @@
   </si>
   <si>
     <t>Settings</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Totem overlay: self tattoo</t>
-  </si>
-  <si>
-    <t>SelfTattoo</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Totem overlay: tattoo enchant</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>TattooEnchant</t>
   </si>
 </sst>
 </file>
@@ -765,13 +690,13 @@
         <v>27</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +716,7 @@
         <v>31</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>18</v>
@@ -852,188 +777,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
